--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-correction.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -51,17 +51,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">保留时输出 2x；随机输出的期望仍为 x。</t>
+          <t xml:space="preserve">保留时为2x，随机输出的期望仍为x。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">输出期望为 2x。</t>
+          <t xml:space="preserve">二者的元素数值期望应该均为2x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">输出以 0.5 概率取 2x、以 0.5 概率取 0，所以 E(y)=x；固定 seed 后得到的是一次确定结果，不是每个位置都取期望。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：2x 是保留分支的一次输出值，不是两个分支加权后的期望。
+• [T#B#计算]：以0.5概率取2x，以0.5概率取0；加权后为x。
+[T#B,!c47f17#边界]：固定 seed 得到一次确定结果，不能要求每个输出都等于期望。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">判断相同 mask 下的输入差异</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两个不同输入使用相同 keep/drop mask 和缩放概率</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">如果差异只在被丢弃的位置，两个输出可以完全相同。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输出结果不同，因为二者来自不同的输入 tensor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Dropout 会抹掉被丢弃位置的输入差异。
+• [T#B#例子]：p=0.5、mask=\[0,1\]；输入\[6,10\]与\[999,10\]都得到\[0,20\]。
+[T#B,!c47f17#边界]：因此不能仅凭输出相同，反推出输入相同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">避免尾部无效 lane 多算一个</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">块长1024，末块只有1个有效 lane</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无效 lane 为1023，满足1024=1+1023。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有效lane数为1，无效数为1024</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：无效数等于块长减有效数，二者之和不能超过这个 program 的总 lane 数。
+• [T#B#核对]：1024−1=1023；无效位置仍是原有1024个 lane 的一部分。
+[T#B,!c47f17#边界]：这里固定块长1024；改变输入长度只改变有效/无效分配，不会额外增加 lane。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">区分保留值与输出期望</t>
+          <t xml:space="preserve">判断同一输入元素经过 inverted dropout 后的随机输出期望。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">p=0.5 的 inverted dropout</t>
+          <t xml:space="preserve">对同一输入 x，以丢弃概率 p=0.5 运行 inverted dropout，并比较两次不同 seed 的调用；两次调用都遵循相同的保留/丢弃概率。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">保留时为2x，随机输出的期望仍为x。</t>
+          <t xml:space="preserve">被保留时的一次输出值是 2x；考虑保留与丢弃两种情况后，随机输出的期望仍为 x。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,26 +61,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：2x 是保留分支的一次输出值，不是两个分支加权后的期望。
-• [T#B#计算]：以0.5概率取2x，以0.5概率取0；加权后为x。
-[T#B,!c47f17#边界]：固定 seed 得到一次确定结果，不能要求每个输出都等于期望。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错误在于把“保留分支的值”当成了“整个随机输出的期望”：期望需要把所有可能结果按概率加权。
+• [T#B#逐项计算]：保留概率为 0.5，输出 x/(1−0.5)=2x；丢弃概率也为 0.5，输出 0。因此期望为 0.5×2x+0.5×0=x。
+• [T#B#两个 seed 的含义]：不同 seed 可以改变某次调用抽到的保留/丢弃结果，但不会把同一个 dropout 概率模型的期望从 x 改为 2x。
+[T#B,!c47f17#边界]：固定 seed 后看到的是一次确定的输出，不应要求这个输出等于期望。也不能把“换了 seed”理解为每个元素都必然改变。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">判断相同 mask 下的输入差异</t>
+          <t xml:space="preserve">判断两个不同输入经过同一个 dropout mask 后，是否一定得到不同输出。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">两个不同输入使用相同 keep/drop mask 和缩放概率</t>
+          <t xml:space="preserve">两个输入 tensor 使用相同的 keep/drop mask、相同丢弃概率 p 和相同计算规则；只改变输入值，观察最终输出是否必须不同。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">如果差异只在被丢弃的位置，两个输出可以完全相同。</t>
+          <t xml:space="preserve">不一定；如果输入差异全部落在被丢弃的位置，差异都会被清零，两个输出可以完全相同。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -90,26 +91,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：Dropout 会抹掉被丢弃位置的输入差异。
-• [T#B#例子]：p=0.5、mask=\[0,1\]；输入\[6,10\]与\[999,10\]都得到\[0,20\]。
-[T#B,!c47f17#边界]：因此不能仅凭输出相同，反推出输入相同。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：相同 mask 只规定哪些位置保留，并不要求不同输入最终仍可区分；dropout 的清零操作会直接抹掉被丢弃位置的差异。
+• [T#B#反例设置]：令 p=0.5，mask=\[0,1\]，其中 0 表示丢弃、1 表示保留。输入分别为 \[6,10\] 和 \[999,10\]，只有第一个位置不同。
+• [T#B#比较结果]：第一个位置都输出 0；第二个位置都输出 10/(1−0.5)=20。所以两个输出均为 \[0,20\]。
+[T#B,!c47f17#边界]：因此“输入不同”不足以推出“dropout 输出不同”，也不能仅凭输出相同就反推输入相同；至少要继续检查被保留位置的输入。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">避免尾部无效 lane 多算一个</t>
+          <t xml:space="preserve">计算分块向量 kernel 最后一个 program 中，有效与无效计算位置的数量。</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">块长1024，末块只有1个有效 lane</t>
+          <t xml:space="preserve">输入长度 n=1025，每个 program 生成 BLOCK_SIZE=1024 个位置；最后一个 program 从 offset=1024 开始，因此只有第一个位置属于输入。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">无效 lane 为1023，满足1024=1+1023。</t>
+          <t xml:space="preserve">末块有效位置为 1 个，无效位置为 1023 个，满足 1024=1+1023。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -119,9 +121,10 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：无效数等于块长减有效数，二者之和不能超过这个 program 的总 lane 数。
-• [T#B#核对]：1024−1=1023；无效位置仍是原有1024个 lane 的一部分。
-[T#B,!c47f17#边界]：这里固定块长1024；改变输入长度只改变有效/无效分配，不会额外增加 lane。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：一个 program 生成的位置总数固定；有效和无效只是把这批位置分成两部分，不会在有效位置之外再额外生成一整块无效位置。
+• [T#B#范围核对]：末块的名义 offset 范围是 \[1024,2048)，共有 1024 个位置；输入有效范围截至 1025，所以这里只有 offset=1024 有效。
+• [T#B#数量核对]：无效数量应为 BLOCK_SIZE−有效数量，即 1024−1=1023。把无效数写成 1024 会令总数变成 1025，与固定块长矛盾。
+[T#B,!c47f17#边界]：这里的 lane 指这组向量化计算中的元素位置，计数依据是 BLOCK_SIZE；不要把它理解成额外新增的 GPU 线程。</t>
         </is>
       </c>
     </row>
